--- a/FM-MN-07_WELDING_ALUMINUM-01.xlsx
+++ b/FM-MN-07_WELDING_ALUMINUM-01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\Maintenance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A20D099F-3608-4452-BF69-2BE57036CBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E13E3F95-3ED3-4E68-B59C-4FC2B107DEBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{20A5A030-5C99-4036-BF6B-54752E5F0EEB}"/>
   </bookViews>
@@ -306,7 +306,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
@@ -352,12 +352,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -379,16 +391,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1444,80 +1447,80 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:33" s="14" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
-      <c r="R1" s="21"/>
-      <c r="S1" s="21"/>
-      <c r="T1" s="21"/>
-      <c r="U1" s="21"/>
-      <c r="V1" s="21"/>
-      <c r="W1" s="21"/>
-      <c r="X1" s="21"/>
-      <c r="Y1" s="21"/>
-      <c r="Z1" s="21"/>
-      <c r="AA1" s="21"/>
-      <c r="AB1" s="22" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
+      <c r="R1" s="25"/>
+      <c r="S1" s="25"/>
+      <c r="T1" s="25"/>
+      <c r="U1" s="25"/>
+      <c r="V1" s="25"/>
+      <c r="W1" s="25"/>
+      <c r="X1" s="25"/>
+      <c r="Y1" s="25"/>
+      <c r="Z1" s="25"/>
+      <c r="AA1" s="25"/>
+      <c r="AB1" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="AC1" s="22"/>
-      <c r="AD1" s="22"/>
-      <c r="AE1" s="22"/>
-      <c r="AF1" s="22"/>
-      <c r="AG1" s="22"/>
+      <c r="AC1" s="26"/>
+      <c r="AD1" s="26"/>
+      <c r="AE1" s="26"/>
+      <c r="AF1" s="26"/>
+      <c r="AG1" s="26"/>
     </row>
     <row r="2" spans="1:33" s="14" customFormat="1" ht="25.5" customHeight="1">
-      <c r="A2" s="21"/>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="21"/>
-      <c r="O2" s="21"/>
-      <c r="P2" s="21"/>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="21"/>
-      <c r="S2" s="21"/>
-      <c r="T2" s="21"/>
-      <c r="U2" s="21"/>
-      <c r="V2" s="21"/>
-      <c r="W2" s="21"/>
-      <c r="X2" s="21"/>
-      <c r="Y2" s="21"/>
-      <c r="Z2" s="21"/>
-      <c r="AA2" s="21"/>
-      <c r="AB2" s="22" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="25"/>
+      <c r="N2" s="25"/>
+      <c r="O2" s="25"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="25"/>
+      <c r="R2" s="25"/>
+      <c r="S2" s="25"/>
+      <c r="T2" s="25"/>
+      <c r="U2" s="25"/>
+      <c r="V2" s="25"/>
+      <c r="W2" s="25"/>
+      <c r="X2" s="25"/>
+      <c r="Y2" s="25"/>
+      <c r="Z2" s="25"/>
+      <c r="AA2" s="25"/>
+      <c r="AB2" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="AC2" s="22"/>
-      <c r="AD2" s="22"/>
-      <c r="AE2" s="22"/>
-      <c r="AF2" s="22"/>
-      <c r="AG2" s="22"/>
+      <c r="AC2" s="26"/>
+      <c r="AD2" s="26"/>
+      <c r="AE2" s="26"/>
+      <c r="AF2" s="26"/>
+      <c r="AG2" s="26"/>
     </row>
     <row r="3" spans="1:33" s="14" customFormat="1" ht="15.75" customHeight="1">
       <c r="A3" s="17"/>
@@ -1555,49 +1558,49 @@
       <c r="AG3" s="15"/>
     </row>
     <row r="4" spans="1:33" s="8" customFormat="1" ht="18" customHeight="1">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="27"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="27"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="27"/>
-      <c r="R4" s="27"/>
-      <c r="S4" s="27"/>
-      <c r="T4" s="27"/>
-      <c r="U4" s="27"/>
-      <c r="V4" s="27"/>
-      <c r="W4" s="27"/>
-      <c r="X4" s="27"/>
-      <c r="Y4" s="27"/>
-      <c r="Z4" s="27"/>
-      <c r="AA4" s="27"/>
-      <c r="AB4" s="27"/>
-      <c r="AC4" s="27"/>
-      <c r="AD4" s="27"/>
-      <c r="AE4" s="27"/>
-      <c r="AF4" s="27"/>
-      <c r="AG4" s="27"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
+      <c r="O4" s="31"/>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="31"/>
+      <c r="S4" s="31"/>
+      <c r="T4" s="31"/>
+      <c r="U4" s="31"/>
+      <c r="V4" s="31"/>
+      <c r="W4" s="31"/>
+      <c r="X4" s="31"/>
+      <c r="Y4" s="31"/>
+      <c r="Z4" s="31"/>
+      <c r="AA4" s="31"/>
+      <c r="AB4" s="31"/>
+      <c r="AC4" s="31"/>
+      <c r="AD4" s="31"/>
+      <c r="AE4" s="31"/>
+      <c r="AF4" s="31"/>
+      <c r="AG4" s="31"/>
     </row>
     <row r="5" spans="1:33" s="8" customFormat="1" ht="13.5" customHeight="1">
-      <c r="A5" s="24"/>
-      <c r="B5" s="26"/>
+      <c r="A5" s="28"/>
+      <c r="B5" s="30"/>
       <c r="C5" s="9">
         <v>1</v>
       </c>
@@ -1968,179 +1971,270 @@
     <row r="13" spans="1:33" ht="22.5" customHeight="1">
       <c r="A13" s="7"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="19"/>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-      <c r="M13" s="19"/>
-      <c r="N13" s="19"/>
-      <c r="O13" s="19"/>
-      <c r="P13" s="19"/>
-      <c r="Q13" s="19"/>
-      <c r="R13" s="19"/>
-      <c r="S13" s="19"/>
-      <c r="T13" s="19"/>
-      <c r="U13" s="19"/>
-      <c r="V13" s="19"/>
-      <c r="W13" s="19"/>
-      <c r="X13" s="19"/>
-      <c r="Y13" s="19"/>
-      <c r="Z13" s="19"/>
-      <c r="AA13" s="19"/>
-      <c r="AB13" s="19"/>
-      <c r="AC13" s="19"/>
-      <c r="AD13" s="19"/>
-      <c r="AE13" s="19"/>
-      <c r="AF13" s="19"/>
-      <c r="AG13" s="19"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="24"/>
+      <c r="K13" s="24"/>
+      <c r="L13" s="24"/>
+      <c r="M13" s="24"/>
+      <c r="N13" s="24"/>
+      <c r="O13" s="24"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="24"/>
+      <c r="R13" s="24"/>
+      <c r="S13" s="24"/>
+      <c r="T13" s="24"/>
+      <c r="U13" s="24"/>
+      <c r="V13" s="24"/>
+      <c r="W13" s="24"/>
+      <c r="X13" s="24"/>
+      <c r="Y13" s="24"/>
+      <c r="Z13" s="24"/>
+      <c r="AA13" s="24"/>
+      <c r="AB13" s="24"/>
+      <c r="AC13" s="24"/>
+      <c r="AD13" s="24"/>
+      <c r="AE13" s="24"/>
+      <c r="AF13" s="24"/>
+      <c r="AG13" s="24"/>
     </row>
     <row r="14" spans="1:33" ht="22.5" customHeight="1">
       <c r="B14" s="5"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="20"/>
-      <c r="L14" s="20"/>
-      <c r="M14" s="20"/>
-      <c r="N14" s="20"/>
-      <c r="O14" s="20"/>
-      <c r="P14" s="20"/>
-      <c r="Q14" s="20"/>
-      <c r="R14" s="20"/>
-      <c r="S14" s="20"/>
-      <c r="T14" s="20"/>
-      <c r="U14" s="20"/>
-      <c r="V14" s="20"/>
-      <c r="W14" s="20"/>
-      <c r="X14" s="20"/>
-      <c r="Y14" s="20"/>
-      <c r="Z14" s="20"/>
-      <c r="AA14" s="20"/>
-      <c r="AB14" s="20"/>
-      <c r="AC14" s="20"/>
-      <c r="AD14" s="20"/>
-      <c r="AE14" s="20"/>
-      <c r="AF14" s="20"/>
-      <c r="AG14" s="20"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="22"/>
+      <c r="P14" s="22"/>
+      <c r="Q14" s="22"/>
+      <c r="R14" s="22"/>
+      <c r="S14" s="22"/>
+      <c r="T14" s="22"/>
+      <c r="U14" s="22"/>
+      <c r="V14" s="22"/>
+      <c r="W14" s="22"/>
+      <c r="X14" s="22"/>
+      <c r="Y14" s="22"/>
+      <c r="Z14" s="22"/>
+      <c r="AA14" s="22"/>
+      <c r="AB14" s="22"/>
+      <c r="AC14" s="22"/>
+      <c r="AD14" s="22"/>
+      <c r="AE14" s="22"/>
+      <c r="AF14" s="22"/>
+      <c r="AG14" s="22"/>
     </row>
     <row r="15" spans="1:33" ht="22.5" customHeight="1">
       <c r="B15" s="5"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="28"/>
-      <c r="K15" s="28"/>
-      <c r="L15" s="28"/>
-      <c r="M15" s="28"/>
-      <c r="N15" s="28"/>
-      <c r="O15" s="28"/>
-      <c r="P15" s="28"/>
-      <c r="Q15" s="28"/>
-      <c r="R15" s="28"/>
-      <c r="S15" s="28"/>
-      <c r="T15" s="28"/>
-      <c r="U15" s="28"/>
-      <c r="V15" s="28"/>
-      <c r="W15" s="28"/>
-      <c r="X15" s="28"/>
-      <c r="Y15" s="28"/>
-      <c r="Z15" s="28"/>
-      <c r="AA15" s="28"/>
-      <c r="AB15" s="28"/>
-      <c r="AC15" s="28"/>
-      <c r="AD15" s="28"/>
-      <c r="AE15" s="28"/>
-      <c r="AF15" s="28"/>
-      <c r="AG15" s="28"/>
+      <c r="C15" s="21"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="21"/>
+      <c r="M15" s="21"/>
+      <c r="N15" s="21"/>
+      <c r="O15" s="21"/>
+      <c r="P15" s="21"/>
+      <c r="Q15" s="21"/>
+      <c r="R15" s="21"/>
+      <c r="S15" s="21"/>
+      <c r="T15" s="21"/>
+      <c r="U15" s="21"/>
+      <c r="V15" s="21"/>
+      <c r="W15" s="21"/>
+      <c r="X15" s="21"/>
+      <c r="Y15" s="21"/>
+      <c r="Z15" s="21"/>
+      <c r="AA15" s="21"/>
+      <c r="AB15" s="21"/>
+      <c r="AC15" s="21"/>
+      <c r="AD15" s="21"/>
+      <c r="AE15" s="21"/>
+      <c r="AF15" s="21"/>
+      <c r="AG15" s="21"/>
     </row>
     <row r="16" spans="1:33" ht="22.5" customHeight="1">
       <c r="B16" s="5"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-      <c r="M16" s="20"/>
-      <c r="N16" s="20"/>
-      <c r="O16" s="20"/>
-      <c r="P16" s="20"/>
-      <c r="Q16" s="20"/>
-      <c r="R16" s="20"/>
-      <c r="S16" s="20"/>
-      <c r="T16" s="20"/>
-      <c r="U16" s="20"/>
-      <c r="V16" s="20"/>
-      <c r="W16" s="20"/>
-      <c r="X16" s="20"/>
-      <c r="Y16" s="20"/>
-      <c r="Z16" s="20"/>
-      <c r="AA16" s="20"/>
-      <c r="AB16" s="20"/>
-      <c r="AC16" s="20"/>
-      <c r="AD16" s="20"/>
-      <c r="AE16" s="20"/>
-      <c r="AF16" s="20"/>
-      <c r="AG16" s="20"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22"/>
+      <c r="R16" s="22"/>
+      <c r="S16" s="22"/>
+      <c r="T16" s="22"/>
+      <c r="U16" s="22"/>
+      <c r="V16" s="22"/>
+      <c r="W16" s="22"/>
+      <c r="X16" s="22"/>
+      <c r="Y16" s="22"/>
+      <c r="Z16" s="22"/>
+      <c r="AA16" s="22"/>
+      <c r="AB16" s="22"/>
+      <c r="AC16" s="22"/>
+      <c r="AD16" s="22"/>
+      <c r="AE16" s="22"/>
+      <c r="AF16" s="22"/>
+      <c r="AG16" s="22"/>
     </row>
     <row r="17" spans="2:33" ht="19.5" customHeight="1">
       <c r="B17" s="18" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="2:33" ht="261.75" customHeight="1"/>
+    <row r="18" spans="2:33" ht="261.75" customHeight="1">
+      <c r="B18" s="32"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="32"/>
+      <c r="K18" s="32"/>
+      <c r="L18" s="32"/>
+      <c r="M18" s="32"/>
+      <c r="N18" s="32"/>
+      <c r="O18" s="32"/>
+      <c r="P18" s="32"/>
+      <c r="Q18" s="32"/>
+      <c r="R18" s="32"/>
+      <c r="S18" s="32"/>
+      <c r="T18" s="32"/>
+      <c r="U18" s="32"/>
+      <c r="V18" s="32"/>
+      <c r="W18" s="32"/>
+      <c r="X18" s="32"/>
+      <c r="Y18" s="32"/>
+      <c r="Z18" s="32"/>
+      <c r="AA18" s="32"/>
+      <c r="AB18" s="32"/>
+      <c r="AC18" s="32"/>
+      <c r="AD18" s="32"/>
+      <c r="AE18" s="32"/>
+      <c r="AF18" s="32"/>
+      <c r="AG18" s="32"/>
+    </row>
     <row r="19" spans="2:33" ht="23.25" customHeight="1"/>
     <row r="20" spans="2:33" ht="23.25" customHeight="1">
       <c r="AB20" s="4"/>
-      <c r="AC20" s="29"/>
-      <c r="AD20" s="29"/>
-      <c r="AE20" s="29"/>
-      <c r="AF20" s="29"/>
-      <c r="AG20" s="29"/>
+      <c r="AC20" s="23"/>
+      <c r="AD20" s="23"/>
+      <c r="AE20" s="23"/>
+      <c r="AF20" s="23"/>
+      <c r="AG20" s="23"/>
     </row>
     <row r="21" spans="2:33" ht="23.25" customHeight="1">
-      <c r="AC21" s="31" t="s">
+      <c r="AC21" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="AD21" s="31"/>
-      <c r="AE21" s="31"/>
-      <c r="AF21" s="31"/>
-      <c r="AG21" s="31"/>
+      <c r="AD21" s="20"/>
+      <c r="AE21" s="20"/>
+      <c r="AF21" s="20"/>
+      <c r="AG21" s="20"/>
     </row>
     <row r="22" spans="2:33" ht="7.5" customHeight="1">
       <c r="D22" s="3"/>
     </row>
     <row r="23" spans="2:33" ht="14.25" customHeight="1">
       <c r="C23" s="2"/>
-      <c r="AC23" s="30" t="s">
+      <c r="AC23" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="AD23" s="30"/>
-      <c r="AE23" s="30"/>
-      <c r="AF23" s="30"/>
-      <c r="AG23" s="30"/>
+      <c r="AD23" s="19"/>
+      <c r="AE23" s="19"/>
+      <c r="AF23" s="19"/>
+      <c r="AG23" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="71">
+  <mergeCells count="72">
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="A1:AA2"/>
+    <mergeCell ref="AB1:AG1"/>
+    <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:AG4"/>
+    <mergeCell ref="V15:V16"/>
+    <mergeCell ref="W15:W16"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="S13:S14"/>
+    <mergeCell ref="T13:T14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="U13:U14"/>
+    <mergeCell ref="V13:V14"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="R15:R16"/>
+    <mergeCell ref="S15:S16"/>
+    <mergeCell ref="T15:T16"/>
+    <mergeCell ref="U15:U16"/>
+    <mergeCell ref="L15:L16"/>
+    <mergeCell ref="M15:M16"/>
+    <mergeCell ref="N15:N16"/>
+    <mergeCell ref="O15:O16"/>
+    <mergeCell ref="P15:P16"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="AG13:AG14"/>
+    <mergeCell ref="AD13:AD14"/>
+    <mergeCell ref="AE13:AE14"/>
+    <mergeCell ref="AF13:AF14"/>
+    <mergeCell ref="R13:R14"/>
+    <mergeCell ref="AA13:AA14"/>
+    <mergeCell ref="AB13:AB14"/>
+    <mergeCell ref="AC13:AC14"/>
+    <mergeCell ref="Z13:Z14"/>
+    <mergeCell ref="W13:W14"/>
+    <mergeCell ref="X13:X14"/>
+    <mergeCell ref="Y13:Y14"/>
     <mergeCell ref="AC23:AG23"/>
     <mergeCell ref="AC21:AG21"/>
     <mergeCell ref="X15:X16"/>
@@ -2154,64 +2248,7 @@
     <mergeCell ref="AF15:AF16"/>
     <mergeCell ref="AG15:AG16"/>
     <mergeCell ref="AC20:AG20"/>
-    <mergeCell ref="AG13:AG14"/>
-    <mergeCell ref="AD13:AD14"/>
-    <mergeCell ref="AE13:AE14"/>
-    <mergeCell ref="AF13:AF14"/>
-    <mergeCell ref="R13:R14"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="R15:R16"/>
-    <mergeCell ref="S15:S16"/>
-    <mergeCell ref="T15:T16"/>
-    <mergeCell ref="U15:U16"/>
-    <mergeCell ref="L15:L16"/>
-    <mergeCell ref="M15:M16"/>
-    <mergeCell ref="N15:N16"/>
-    <mergeCell ref="O15:O16"/>
-    <mergeCell ref="P15:P16"/>
-    <mergeCell ref="Q15:Q16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="AA13:AA14"/>
-    <mergeCell ref="AB13:AB14"/>
-    <mergeCell ref="AC13:AC14"/>
-    <mergeCell ref="Z13:Z14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="U13:U14"/>
-    <mergeCell ref="V13:V14"/>
-    <mergeCell ref="W13:W14"/>
-    <mergeCell ref="X13:X14"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="K15:K16"/>
-    <mergeCell ref="V15:V16"/>
-    <mergeCell ref="W15:W16"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="S13:S14"/>
-    <mergeCell ref="T13:T14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="A1:AA2"/>
-    <mergeCell ref="AB1:AG1"/>
-    <mergeCell ref="AB2:AG2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:AG4"/>
-    <mergeCell ref="Y13:Y14"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="B18:AG18"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>

--- a/FM-MN-07_WELDING_ALUMINUM-01.xlsx
+++ b/FM-MN-07_WELDING_ALUMINUM-01.xlsx
@@ -297,7 +297,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -396,6 +396,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1734,8 +1737,16 @@
       <c r="AB6" s="9" t="n"/>
       <c r="AC6" s="9" t="n"/>
       <c r="AD6" s="9" t="n"/>
-      <c r="AE6" s="9" t="n"/>
-      <c r="AF6" s="9" t="n"/>
+      <c r="AE6" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF6" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG6" s="9" t="n"/>
     </row>
     <row r="7" ht="15.75" customFormat="1" customHeight="1" s="8">
@@ -1775,8 +1786,16 @@
       <c r="AB7" s="9" t="n"/>
       <c r="AC7" s="9" t="n"/>
       <c r="AD7" s="9" t="n"/>
-      <c r="AE7" s="9" t="n"/>
-      <c r="AF7" s="9" t="n"/>
+      <c r="AE7" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF7" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG7" s="9" t="n"/>
     </row>
     <row r="8" ht="15.75" customFormat="1" customHeight="1" s="8">
@@ -1816,8 +1835,16 @@
       <c r="AB8" s="9" t="n"/>
       <c r="AC8" s="9" t="n"/>
       <c r="AD8" s="9" t="n"/>
-      <c r="AE8" s="9" t="n"/>
-      <c r="AF8" s="9" t="n"/>
+      <c r="AE8" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF8" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG8" s="9" t="n"/>
     </row>
     <row r="9" ht="15.75" customFormat="1" customHeight="1" s="8">
@@ -1857,8 +1884,16 @@
       <c r="AB9" s="9" t="n"/>
       <c r="AC9" s="9" t="n"/>
       <c r="AD9" s="9" t="n"/>
-      <c r="AE9" s="9" t="n"/>
-      <c r="AF9" s="9" t="n"/>
+      <c r="AE9" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF9" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG9" s="9" t="n"/>
     </row>
     <row r="10" ht="15.75" customFormat="1" customHeight="1" s="8">
@@ -1898,8 +1933,16 @@
       <c r="AB10" s="9" t="n"/>
       <c r="AC10" s="9" t="n"/>
       <c r="AD10" s="9" t="n"/>
-      <c r="AE10" s="9" t="n"/>
-      <c r="AF10" s="9" t="n"/>
+      <c r="AE10" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF10" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG10" s="9" t="n"/>
     </row>
     <row r="11" ht="15.75" customFormat="1" customHeight="1" s="8">
@@ -1939,8 +1982,16 @@
       <c r="AB11" s="9" t="n"/>
       <c r="AC11" s="9" t="n"/>
       <c r="AD11" s="9" t="n"/>
-      <c r="AE11" s="9" t="n"/>
-      <c r="AF11" s="9" t="n"/>
+      <c r="AE11" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF11" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG11" s="9" t="n"/>
     </row>
     <row r="12" ht="15.75" customFormat="1" customHeight="1" s="8">
@@ -1980,8 +2031,16 @@
       <c r="AB12" s="9" t="n"/>
       <c r="AC12" s="9" t="n"/>
       <c r="AD12" s="9" t="n"/>
-      <c r="AE12" s="9" t="n"/>
-      <c r="AF12" s="9" t="n"/>
+      <c r="AE12" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
+      <c r="AF12" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="AG12" s="9" t="n"/>
     </row>
     <row r="13" ht="22.5" customHeight="1">
@@ -2015,8 +2074,16 @@
       <c r="AB13" s="38" t="n"/>
       <c r="AC13" s="38" t="n"/>
       <c r="AD13" s="38" t="n"/>
-      <c r="AE13" s="38" t="n"/>
-      <c r="AF13" s="38" t="n"/>
+      <c r="AE13" s="40" t="inlineStr">
+        <is>
+          <t>ธนุช สิงห์เถื่อน</t>
+        </is>
+      </c>
+      <c r="AF13" s="40" t="inlineStr">
+        <is>
+          <t>อินทัช เป็นสุข</t>
+        </is>
+      </c>
       <c r="AG13" s="38" t="n"/>
     </row>
     <row r="14" ht="22.5" customHeight="1">
@@ -2129,7 +2196,7 @@
       </c>
     </row>
     <row r="18" ht="261.75" customHeight="1">
-      <c r="B18" s="32" t="n"/>
+      <c r="B18" s="32" t="inlineStr"/>
     </row>
     <row r="19" ht="23.25" customHeight="1"/>
     <row r="20" ht="23.25" customHeight="1">
@@ -2162,8 +2229,8 @@
   <mergeCells count="72">
     <mergeCell ref="W15:W16"/>
     <mergeCell ref="F15:F16"/>
+    <mergeCell ref="AB1:AG1"/>
     <mergeCell ref="Y15:Y16"/>
-    <mergeCell ref="AB1:AG1"/>
     <mergeCell ref="J13:J14"/>
     <mergeCell ref="L13:L14"/>
     <mergeCell ref="R13:R14"/>

--- a/FM-MN-07_WELDING_ALUMINUM-01.xlsx
+++ b/FM-MN-07_WELDING_ALUMINUM-01.xlsx
@@ -297,7 +297,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
@@ -398,6 +398,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1709,45 +1712,37 @@
           <t>ตรวจสภาพความพรัอมโดยรวมของเครื่อง</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n"/>
-      <c r="D6" s="9" t="n"/>
-      <c r="E6" s="9" t="n"/>
-      <c r="F6" s="9" t="n"/>
-      <c r="G6" s="9" t="n"/>
-      <c r="H6" s="9" t="n"/>
-      <c r="I6" s="9" t="n"/>
-      <c r="J6" s="9" t="n"/>
-      <c r="K6" s="9" t="n"/>
-      <c r="L6" s="9" t="n"/>
-      <c r="M6" s="9" t="n"/>
-      <c r="N6" s="9" t="n"/>
-      <c r="O6" s="9" t="n"/>
-      <c r="P6" s="9" t="n"/>
-      <c r="Q6" s="9" t="n"/>
-      <c r="R6" s="9" t="n"/>
-      <c r="S6" s="9" t="n"/>
-      <c r="T6" s="9" t="n"/>
-      <c r="U6" s="9" t="n"/>
-      <c r="V6" s="9" t="n"/>
-      <c r="W6" s="9" t="n"/>
-      <c r="X6" s="9" t="n"/>
-      <c r="Y6" s="9" t="n"/>
-      <c r="Z6" s="9" t="n"/>
-      <c r="AA6" s="9" t="n"/>
-      <c r="AB6" s="9" t="n"/>
-      <c r="AC6" s="9" t="n"/>
-      <c r="AD6" s="9" t="n"/>
-      <c r="AE6" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF6" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG6" s="9" t="n"/>
+      <c r="C6" s="9" t="inlineStr"/>
+      <c r="D6" s="9" t="inlineStr"/>
+      <c r="E6" s="9" t="inlineStr"/>
+      <c r="F6" s="9" t="inlineStr"/>
+      <c r="G6" s="9" t="inlineStr"/>
+      <c r="H6" s="9" t="inlineStr"/>
+      <c r="I6" s="9" t="inlineStr"/>
+      <c r="J6" s="9" t="inlineStr"/>
+      <c r="K6" s="9" t="inlineStr"/>
+      <c r="L6" s="9" t="inlineStr"/>
+      <c r="M6" s="9" t="inlineStr"/>
+      <c r="N6" s="9" t="inlineStr"/>
+      <c r="O6" s="9" t="inlineStr"/>
+      <c r="P6" s="9" t="inlineStr"/>
+      <c r="Q6" s="9" t="inlineStr"/>
+      <c r="R6" s="9" t="inlineStr"/>
+      <c r="S6" s="9" t="inlineStr"/>
+      <c r="T6" s="9" t="inlineStr"/>
+      <c r="U6" s="9" t="inlineStr"/>
+      <c r="V6" s="9" t="inlineStr"/>
+      <c r="W6" s="9" t="inlineStr"/>
+      <c r="X6" s="9" t="inlineStr"/>
+      <c r="Y6" s="9" t="inlineStr"/>
+      <c r="Z6" s="9" t="inlineStr"/>
+      <c r="AA6" s="9" t="inlineStr"/>
+      <c r="AB6" s="9" t="inlineStr"/>
+      <c r="AC6" s="9" t="inlineStr"/>
+      <c r="AD6" s="9" t="inlineStr"/>
+      <c r="AE6" s="9" t="inlineStr"/>
+      <c r="AF6" s="9" t="inlineStr"/>
+      <c r="AG6" s="9" t="inlineStr"/>
     </row>
     <row r="7" ht="15.75" customFormat="1" customHeight="1" s="8">
       <c r="A7" s="11" t="n">
@@ -1758,45 +1753,37 @@
           <t xml:space="preserve">เช็ค  BREAKER  เพื่อเช็คระบบไฟฟ้า ตามตำแหน่งไฟ โชว์  และ SWITCH  ต่าง ๆ </t>
         </is>
       </c>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="9" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="9" t="n"/>
-      <c r="G7" s="9" t="n"/>
-      <c r="H7" s="9" t="n"/>
-      <c r="I7" s="9" t="n"/>
-      <c r="J7" s="9" t="n"/>
-      <c r="K7" s="9" t="n"/>
-      <c r="L7" s="9" t="n"/>
-      <c r="M7" s="9" t="n"/>
-      <c r="N7" s="9" t="n"/>
-      <c r="O7" s="9" t="n"/>
-      <c r="P7" s="9" t="n"/>
-      <c r="Q7" s="9" t="n"/>
-      <c r="R7" s="9" t="n"/>
-      <c r="S7" s="9" t="n"/>
-      <c r="T7" s="9" t="n"/>
-      <c r="U7" s="9" t="n"/>
-      <c r="V7" s="9" t="n"/>
-      <c r="W7" s="9" t="n"/>
-      <c r="X7" s="9" t="n"/>
-      <c r="Y7" s="9" t="n"/>
-      <c r="Z7" s="9" t="n"/>
-      <c r="AA7" s="9" t="n"/>
-      <c r="AB7" s="9" t="n"/>
-      <c r="AC7" s="9" t="n"/>
-      <c r="AD7" s="9" t="n"/>
-      <c r="AE7" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF7" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG7" s="9" t="n"/>
+      <c r="C7" s="9" t="inlineStr"/>
+      <c r="D7" s="9" t="inlineStr"/>
+      <c r="E7" s="9" t="inlineStr"/>
+      <c r="F7" s="9" t="inlineStr"/>
+      <c r="G7" s="9" t="inlineStr"/>
+      <c r="H7" s="9" t="inlineStr"/>
+      <c r="I7" s="9" t="inlineStr"/>
+      <c r="J7" s="9" t="inlineStr"/>
+      <c r="K7" s="9" t="inlineStr"/>
+      <c r="L7" s="9" t="inlineStr"/>
+      <c r="M7" s="9" t="inlineStr"/>
+      <c r="N7" s="9" t="inlineStr"/>
+      <c r="O7" s="9" t="inlineStr"/>
+      <c r="P7" s="9" t="inlineStr"/>
+      <c r="Q7" s="9" t="inlineStr"/>
+      <c r="R7" s="9" t="inlineStr"/>
+      <c r="S7" s="9" t="inlineStr"/>
+      <c r="T7" s="9" t="inlineStr"/>
+      <c r="U7" s="9" t="inlineStr"/>
+      <c r="V7" s="9" t="inlineStr"/>
+      <c r="W7" s="9" t="inlineStr"/>
+      <c r="X7" s="9" t="inlineStr"/>
+      <c r="Y7" s="9" t="inlineStr"/>
+      <c r="Z7" s="9" t="inlineStr"/>
+      <c r="AA7" s="9" t="inlineStr"/>
+      <c r="AB7" s="9" t="inlineStr"/>
+      <c r="AC7" s="9" t="inlineStr"/>
+      <c r="AD7" s="9" t="inlineStr"/>
+      <c r="AE7" s="9" t="inlineStr"/>
+      <c r="AF7" s="9" t="inlineStr"/>
+      <c r="AG7" s="9" t="inlineStr"/>
     </row>
     <row r="8" ht="15.75" customFormat="1" customHeight="1" s="8">
       <c r="A8" s="11" t="n">
@@ -1807,45 +1794,37 @@
           <t>ตรวจสภาพความพร้อมของสายกราวด์ให้อยู่ในสภาพ ความพร้อมอยู่เสมอ</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="9" t="n"/>
-      <c r="F8" s="9" t="n"/>
-      <c r="G8" s="9" t="n"/>
-      <c r="H8" s="9" t="n"/>
-      <c r="I8" s="9" t="n"/>
-      <c r="J8" s="9" t="n"/>
-      <c r="K8" s="9" t="n"/>
-      <c r="L8" s="9" t="n"/>
-      <c r="M8" s="9" t="n"/>
-      <c r="N8" s="9" t="n"/>
-      <c r="O8" s="9" t="n"/>
-      <c r="P8" s="9" t="n"/>
-      <c r="Q8" s="9" t="n"/>
-      <c r="R8" s="9" t="n"/>
-      <c r="S8" s="9" t="n"/>
-      <c r="T8" s="9" t="n"/>
-      <c r="U8" s="9" t="n"/>
-      <c r="V8" s="9" t="n"/>
-      <c r="W8" s="9" t="n"/>
-      <c r="X8" s="9" t="n"/>
-      <c r="Y8" s="9" t="n"/>
-      <c r="Z8" s="9" t="n"/>
-      <c r="AA8" s="9" t="n"/>
-      <c r="AB8" s="9" t="n"/>
-      <c r="AC8" s="9" t="n"/>
-      <c r="AD8" s="9" t="n"/>
-      <c r="AE8" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF8" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG8" s="9" t="n"/>
+      <c r="C8" s="9" t="inlineStr"/>
+      <c r="D8" s="9" t="inlineStr"/>
+      <c r="E8" s="9" t="inlineStr"/>
+      <c r="F8" s="9" t="inlineStr"/>
+      <c r="G8" s="9" t="inlineStr"/>
+      <c r="H8" s="9" t="inlineStr"/>
+      <c r="I8" s="9" t="inlineStr"/>
+      <c r="J8" s="9" t="inlineStr"/>
+      <c r="K8" s="9" t="inlineStr"/>
+      <c r="L8" s="9" t="inlineStr"/>
+      <c r="M8" s="9" t="inlineStr"/>
+      <c r="N8" s="9" t="inlineStr"/>
+      <c r="O8" s="9" t="inlineStr"/>
+      <c r="P8" s="9" t="inlineStr"/>
+      <c r="Q8" s="9" t="inlineStr"/>
+      <c r="R8" s="9" t="inlineStr"/>
+      <c r="S8" s="9" t="inlineStr"/>
+      <c r="T8" s="9" t="inlineStr"/>
+      <c r="U8" s="9" t="inlineStr"/>
+      <c r="V8" s="9" t="inlineStr"/>
+      <c r="W8" s="9" t="inlineStr"/>
+      <c r="X8" s="9" t="inlineStr"/>
+      <c r="Y8" s="9" t="inlineStr"/>
+      <c r="Z8" s="9" t="inlineStr"/>
+      <c r="AA8" s="9" t="inlineStr"/>
+      <c r="AB8" s="9" t="inlineStr"/>
+      <c r="AC8" s="9" t="inlineStr"/>
+      <c r="AD8" s="9" t="inlineStr"/>
+      <c r="AE8" s="9" t="inlineStr"/>
+      <c r="AF8" s="9" t="inlineStr"/>
+      <c r="AG8" s="9" t="inlineStr"/>
     </row>
     <row r="9" ht="15.75" customFormat="1" customHeight="1" s="8">
       <c r="A9" s="11" t="n">
@@ -1856,45 +1835,37 @@
           <t>ตรวจจุดต่อของสายท่อแก๊สว่ารั่วหรือไม่</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="9" t="n"/>
-      <c r="G9" s="9" t="n"/>
-      <c r="H9" s="9" t="n"/>
-      <c r="I9" s="9" t="n"/>
-      <c r="J9" s="9" t="n"/>
-      <c r="K9" s="9" t="n"/>
-      <c r="L9" s="9" t="n"/>
-      <c r="M9" s="9" t="n"/>
-      <c r="N9" s="9" t="n"/>
-      <c r="O9" s="9" t="n"/>
-      <c r="P9" s="9" t="n"/>
-      <c r="Q9" s="9" t="n"/>
-      <c r="R9" s="9" t="n"/>
-      <c r="S9" s="9" t="n"/>
-      <c r="T9" s="9" t="n"/>
-      <c r="U9" s="9" t="n"/>
-      <c r="V9" s="9" t="n"/>
-      <c r="W9" s="9" t="n"/>
-      <c r="X9" s="9" t="n"/>
-      <c r="Y9" s="9" t="n"/>
-      <c r="Z9" s="9" t="n"/>
-      <c r="AA9" s="9" t="n"/>
-      <c r="AB9" s="9" t="n"/>
-      <c r="AC9" s="9" t="n"/>
-      <c r="AD9" s="9" t="n"/>
-      <c r="AE9" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF9" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG9" s="9" t="n"/>
+      <c r="C9" s="9" t="inlineStr"/>
+      <c r="D9" s="9" t="inlineStr"/>
+      <c r="E9" s="9" t="inlineStr"/>
+      <c r="F9" s="9" t="inlineStr"/>
+      <c r="G9" s="9" t="inlineStr"/>
+      <c r="H9" s="9" t="inlineStr"/>
+      <c r="I9" s="9" t="inlineStr"/>
+      <c r="J9" s="9" t="inlineStr"/>
+      <c r="K9" s="9" t="inlineStr"/>
+      <c r="L9" s="9" t="inlineStr"/>
+      <c r="M9" s="9" t="inlineStr"/>
+      <c r="N9" s="9" t="inlineStr"/>
+      <c r="O9" s="9" t="inlineStr"/>
+      <c r="P9" s="9" t="inlineStr"/>
+      <c r="Q9" s="9" t="inlineStr"/>
+      <c r="R9" s="9" t="inlineStr"/>
+      <c r="S9" s="9" t="inlineStr"/>
+      <c r="T9" s="9" t="inlineStr"/>
+      <c r="U9" s="9" t="inlineStr"/>
+      <c r="V9" s="9" t="inlineStr"/>
+      <c r="W9" s="9" t="inlineStr"/>
+      <c r="X9" s="9" t="inlineStr"/>
+      <c r="Y9" s="9" t="inlineStr"/>
+      <c r="Z9" s="9" t="inlineStr"/>
+      <c r="AA9" s="9" t="inlineStr"/>
+      <c r="AB9" s="9" t="inlineStr"/>
+      <c r="AC9" s="9" t="inlineStr"/>
+      <c r="AD9" s="9" t="inlineStr"/>
+      <c r="AE9" s="9" t="inlineStr"/>
+      <c r="AF9" s="9" t="inlineStr"/>
+      <c r="AG9" s="9" t="inlineStr"/>
     </row>
     <row r="10" ht="15.75" customFormat="1" customHeight="1" s="8">
       <c r="A10" s="11" t="n">
@@ -1905,45 +1876,37 @@
           <t>เช็คระดับน้ำหล่อเย็นให้อยู่ในระดับพร้อมใช้งาน</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="9" t="n"/>
-      <c r="G10" s="9" t="n"/>
-      <c r="H10" s="9" t="n"/>
-      <c r="I10" s="9" t="n"/>
-      <c r="J10" s="9" t="n"/>
-      <c r="K10" s="9" t="n"/>
-      <c r="L10" s="9" t="n"/>
-      <c r="M10" s="9" t="n"/>
-      <c r="N10" s="9" t="n"/>
-      <c r="O10" s="9" t="n"/>
-      <c r="P10" s="9" t="n"/>
-      <c r="Q10" s="9" t="n"/>
-      <c r="R10" s="9" t="n"/>
-      <c r="S10" s="9" t="n"/>
-      <c r="T10" s="9" t="n"/>
-      <c r="U10" s="9" t="n"/>
-      <c r="V10" s="9" t="n"/>
-      <c r="W10" s="9" t="n"/>
-      <c r="X10" s="9" t="n"/>
-      <c r="Y10" s="9" t="n"/>
-      <c r="Z10" s="9" t="n"/>
-      <c r="AA10" s="9" t="n"/>
-      <c r="AB10" s="9" t="n"/>
-      <c r="AC10" s="9" t="n"/>
-      <c r="AD10" s="9" t="n"/>
-      <c r="AE10" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF10" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG10" s="9" t="n"/>
+      <c r="C10" s="9" t="inlineStr"/>
+      <c r="D10" s="9" t="inlineStr"/>
+      <c r="E10" s="9" t="inlineStr"/>
+      <c r="F10" s="9" t="inlineStr"/>
+      <c r="G10" s="9" t="inlineStr"/>
+      <c r="H10" s="9" t="inlineStr"/>
+      <c r="I10" s="9" t="inlineStr"/>
+      <c r="J10" s="9" t="inlineStr"/>
+      <c r="K10" s="9" t="inlineStr"/>
+      <c r="L10" s="9" t="inlineStr"/>
+      <c r="M10" s="9" t="inlineStr"/>
+      <c r="N10" s="9" t="inlineStr"/>
+      <c r="O10" s="9" t="inlineStr"/>
+      <c r="P10" s="9" t="inlineStr"/>
+      <c r="Q10" s="9" t="inlineStr"/>
+      <c r="R10" s="9" t="inlineStr"/>
+      <c r="S10" s="9" t="inlineStr"/>
+      <c r="T10" s="9" t="inlineStr"/>
+      <c r="U10" s="9" t="inlineStr"/>
+      <c r="V10" s="9" t="inlineStr"/>
+      <c r="W10" s="9" t="inlineStr"/>
+      <c r="X10" s="9" t="inlineStr"/>
+      <c r="Y10" s="9" t="inlineStr"/>
+      <c r="Z10" s="9" t="inlineStr"/>
+      <c r="AA10" s="9" t="inlineStr"/>
+      <c r="AB10" s="9" t="inlineStr"/>
+      <c r="AC10" s="9" t="inlineStr"/>
+      <c r="AD10" s="9" t="inlineStr"/>
+      <c r="AE10" s="9" t="inlineStr"/>
+      <c r="AF10" s="9" t="inlineStr"/>
+      <c r="AG10" s="9" t="inlineStr"/>
     </row>
     <row r="11" ht="15.75" customFormat="1" customHeight="1" s="8">
       <c r="A11" s="11" t="n">
@@ -1954,45 +1917,37 @@
           <t>เช็คระดับแรงดันในถังแก๊สให้พร้อมใช้งาน</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="9" t="n"/>
-      <c r="G11" s="9" t="n"/>
-      <c r="H11" s="9" t="n"/>
-      <c r="I11" s="9" t="n"/>
-      <c r="J11" s="9" t="n"/>
-      <c r="K11" s="9" t="n"/>
-      <c r="L11" s="9" t="n"/>
-      <c r="M11" s="9" t="n"/>
-      <c r="N11" s="9" t="n"/>
-      <c r="O11" s="9" t="n"/>
-      <c r="P11" s="9" t="n"/>
-      <c r="Q11" s="9" t="n"/>
-      <c r="R11" s="9" t="n"/>
-      <c r="S11" s="9" t="n"/>
-      <c r="T11" s="9" t="n"/>
-      <c r="U11" s="9" t="n"/>
-      <c r="V11" s="9" t="n"/>
-      <c r="W11" s="9" t="n"/>
-      <c r="X11" s="9" t="n"/>
-      <c r="Y11" s="9" t="n"/>
-      <c r="Z11" s="9" t="n"/>
-      <c r="AA11" s="9" t="n"/>
-      <c r="AB11" s="9" t="n"/>
-      <c r="AC11" s="9" t="n"/>
-      <c r="AD11" s="9" t="n"/>
-      <c r="AE11" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF11" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG11" s="9" t="n"/>
+      <c r="C11" s="9" t="inlineStr"/>
+      <c r="D11" s="9" t="inlineStr"/>
+      <c r="E11" s="9" t="inlineStr"/>
+      <c r="F11" s="9" t="inlineStr"/>
+      <c r="G11" s="9" t="inlineStr"/>
+      <c r="H11" s="9" t="inlineStr"/>
+      <c r="I11" s="9" t="inlineStr"/>
+      <c r="J11" s="9" t="inlineStr"/>
+      <c r="K11" s="9" t="inlineStr"/>
+      <c r="L11" s="9" t="inlineStr"/>
+      <c r="M11" s="9" t="inlineStr"/>
+      <c r="N11" s="9" t="inlineStr"/>
+      <c r="O11" s="9" t="inlineStr"/>
+      <c r="P11" s="9" t="inlineStr"/>
+      <c r="Q11" s="9" t="inlineStr"/>
+      <c r="R11" s="9" t="inlineStr"/>
+      <c r="S11" s="9" t="inlineStr"/>
+      <c r="T11" s="9" t="inlineStr"/>
+      <c r="U11" s="9" t="inlineStr"/>
+      <c r="V11" s="9" t="inlineStr"/>
+      <c r="W11" s="9" t="inlineStr"/>
+      <c r="X11" s="9" t="inlineStr"/>
+      <c r="Y11" s="9" t="inlineStr"/>
+      <c r="Z11" s="9" t="inlineStr"/>
+      <c r="AA11" s="9" t="inlineStr"/>
+      <c r="AB11" s="9" t="inlineStr"/>
+      <c r="AC11" s="9" t="inlineStr"/>
+      <c r="AD11" s="9" t="inlineStr"/>
+      <c r="AE11" s="9" t="inlineStr"/>
+      <c r="AF11" s="9" t="inlineStr"/>
+      <c r="AG11" s="9" t="inlineStr"/>
     </row>
     <row r="12" ht="15.75" customFormat="1" customHeight="1" s="8">
       <c r="A12" s="11" t="n">
@@ -2003,88 +1958,72 @@
           <t>ทำความสะอาดชุดหัวเชื่อมก่อนใช้งานอย่างสม่ำเสมอ</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="9" t="n"/>
-      <c r="G12" s="9" t="n"/>
-      <c r="H12" s="9" t="n"/>
-      <c r="I12" s="9" t="n"/>
-      <c r="J12" s="9" t="n"/>
-      <c r="K12" s="9" t="n"/>
-      <c r="L12" s="9" t="n"/>
-      <c r="M12" s="9" t="n"/>
-      <c r="N12" s="9" t="n"/>
-      <c r="O12" s="9" t="n"/>
-      <c r="P12" s="9" t="n"/>
-      <c r="Q12" s="9" t="n"/>
-      <c r="R12" s="9" t="n"/>
-      <c r="S12" s="9" t="n"/>
-      <c r="T12" s="9" t="n"/>
-      <c r="U12" s="9" t="n"/>
-      <c r="V12" s="9" t="n"/>
-      <c r="W12" s="9" t="n"/>
-      <c r="X12" s="9" t="n"/>
-      <c r="Y12" s="9" t="n"/>
-      <c r="Z12" s="9" t="n"/>
-      <c r="AA12" s="9" t="n"/>
-      <c r="AB12" s="9" t="n"/>
-      <c r="AC12" s="9" t="n"/>
-      <c r="AD12" s="9" t="n"/>
-      <c r="AE12" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AF12" s="9" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="AG12" s="9" t="n"/>
+      <c r="C12" s="9" t="inlineStr"/>
+      <c r="D12" s="9" t="inlineStr"/>
+      <c r="E12" s="9" t="inlineStr"/>
+      <c r="F12" s="9" t="inlineStr"/>
+      <c r="G12" s="9" t="inlineStr"/>
+      <c r="H12" s="9" t="inlineStr"/>
+      <c r="I12" s="9" t="inlineStr"/>
+      <c r="J12" s="9" t="inlineStr"/>
+      <c r="K12" s="9" t="inlineStr"/>
+      <c r="L12" s="9" t="inlineStr"/>
+      <c r="M12" s="9" t="inlineStr"/>
+      <c r="N12" s="9" t="inlineStr"/>
+      <c r="O12" s="9" t="inlineStr"/>
+      <c r="P12" s="9" t="inlineStr"/>
+      <c r="Q12" s="9" t="inlineStr"/>
+      <c r="R12" s="9" t="inlineStr"/>
+      <c r="S12" s="9" t="inlineStr"/>
+      <c r="T12" s="9" t="inlineStr"/>
+      <c r="U12" s="9" t="inlineStr"/>
+      <c r="V12" s="9" t="inlineStr"/>
+      <c r="W12" s="9" t="inlineStr"/>
+      <c r="X12" s="9" t="inlineStr"/>
+      <c r="Y12" s="9" t="inlineStr"/>
+      <c r="Z12" s="9" t="inlineStr"/>
+      <c r="AA12" s="9" t="inlineStr"/>
+      <c r="AB12" s="9" t="inlineStr"/>
+      <c r="AC12" s="9" t="inlineStr"/>
+      <c r="AD12" s="9" t="inlineStr"/>
+      <c r="AE12" s="9" t="inlineStr"/>
+      <c r="AF12" s="9" t="inlineStr"/>
+      <c r="AG12" s="9" t="inlineStr"/>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="7" t="n"/>
       <c r="B13" s="6" t="n"/>
-      <c r="C13" s="38" t="n"/>
-      <c r="D13" s="38" t="n"/>
-      <c r="E13" s="38" t="n"/>
-      <c r="F13" s="38" t="n"/>
-      <c r="G13" s="38" t="n"/>
-      <c r="H13" s="38" t="n"/>
-      <c r="I13" s="38" t="n"/>
-      <c r="J13" s="38" t="n"/>
-      <c r="K13" s="38" t="n"/>
-      <c r="L13" s="38" t="n"/>
-      <c r="M13" s="38" t="n"/>
-      <c r="N13" s="38" t="n"/>
-      <c r="O13" s="38" t="n"/>
-      <c r="P13" s="38" t="n"/>
-      <c r="Q13" s="38" t="n"/>
-      <c r="R13" s="38" t="n"/>
-      <c r="S13" s="38" t="n"/>
-      <c r="T13" s="38" t="n"/>
-      <c r="U13" s="38" t="n"/>
-      <c r="V13" s="38" t="n"/>
-      <c r="W13" s="38" t="n"/>
-      <c r="X13" s="38" t="n"/>
-      <c r="Y13" s="38" t="n"/>
-      <c r="Z13" s="38" t="n"/>
-      <c r="AA13" s="38" t="n"/>
-      <c r="AB13" s="38" t="n"/>
-      <c r="AC13" s="38" t="n"/>
-      <c r="AD13" s="38" t="n"/>
-      <c r="AE13" s="40" t="inlineStr">
-        <is>
-          <t>ธนุช สิงห์เถื่อน</t>
-        </is>
-      </c>
-      <c r="AF13" s="40" t="inlineStr">
-        <is>
-          <t>อินทัช เป็นสุข</t>
-        </is>
-      </c>
-      <c r="AG13" s="38" t="n"/>
+      <c r="C13" s="38" t="inlineStr"/>
+      <c r="D13" s="38" t="inlineStr"/>
+      <c r="E13" s="38" t="inlineStr"/>
+      <c r="F13" s="38" t="inlineStr"/>
+      <c r="G13" s="38" t="inlineStr"/>
+      <c r="H13" s="38" t="inlineStr"/>
+      <c r="I13" s="38" t="inlineStr"/>
+      <c r="J13" s="38" t="inlineStr"/>
+      <c r="K13" s="38" t="inlineStr"/>
+      <c r="L13" s="38" t="inlineStr"/>
+      <c r="M13" s="38" t="inlineStr"/>
+      <c r="N13" s="38" t="inlineStr"/>
+      <c r="O13" s="38" t="inlineStr"/>
+      <c r="P13" s="38" t="inlineStr"/>
+      <c r="Q13" s="38" t="inlineStr"/>
+      <c r="R13" s="38" t="inlineStr"/>
+      <c r="S13" s="38" t="inlineStr"/>
+      <c r="T13" s="38" t="inlineStr"/>
+      <c r="U13" s="38" t="inlineStr"/>
+      <c r="V13" s="38" t="inlineStr"/>
+      <c r="W13" s="38" t="inlineStr"/>
+      <c r="X13" s="38" t="inlineStr"/>
+      <c r="Y13" s="38" t="inlineStr"/>
+      <c r="Z13" s="38" t="inlineStr"/>
+      <c r="AA13" s="38" t="inlineStr"/>
+      <c r="AB13" s="38" t="inlineStr"/>
+      <c r="AC13" s="38" t="inlineStr"/>
+      <c r="AD13" s="38" t="inlineStr"/>
+      <c r="AE13" s="40" t="inlineStr"/>
+      <c r="AF13" s="40" t="inlineStr"/>
+      <c r="AG13" s="38" t="inlineStr"/>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="B14" s="5" t="n"/>
@@ -2122,37 +2061,37 @@
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="B15" s="5" t="n"/>
-      <c r="C15" s="22" t="n"/>
-      <c r="D15" s="22" t="n"/>
-      <c r="E15" s="22" t="n"/>
-      <c r="F15" s="22" t="n"/>
-      <c r="G15" s="22" t="n"/>
-      <c r="H15" s="22" t="n"/>
-      <c r="I15" s="22" t="n"/>
-      <c r="J15" s="22" t="n"/>
-      <c r="K15" s="22" t="n"/>
-      <c r="L15" s="22" t="n"/>
-      <c r="M15" s="22" t="n"/>
-      <c r="N15" s="22" t="n"/>
-      <c r="O15" s="22" t="n"/>
-      <c r="P15" s="22" t="n"/>
-      <c r="Q15" s="22" t="n"/>
-      <c r="R15" s="22" t="n"/>
-      <c r="S15" s="22" t="n"/>
-      <c r="T15" s="22" t="n"/>
-      <c r="U15" s="22" t="n"/>
-      <c r="V15" s="22" t="n"/>
-      <c r="W15" s="22" t="n"/>
-      <c r="X15" s="22" t="n"/>
-      <c r="Y15" s="22" t="n"/>
-      <c r="Z15" s="22" t="n"/>
-      <c r="AA15" s="22" t="n"/>
-      <c r="AB15" s="22" t="n"/>
-      <c r="AC15" s="22" t="n"/>
-      <c r="AD15" s="22" t="n"/>
-      <c r="AE15" s="22" t="n"/>
-      <c r="AF15" s="22" t="n"/>
-      <c r="AG15" s="22" t="n"/>
+      <c r="C15" s="22" t="inlineStr"/>
+      <c r="D15" s="22" t="inlineStr"/>
+      <c r="E15" s="22" t="inlineStr"/>
+      <c r="F15" s="22" t="inlineStr"/>
+      <c r="G15" s="22" t="inlineStr"/>
+      <c r="H15" s="22" t="inlineStr"/>
+      <c r="I15" s="22" t="inlineStr"/>
+      <c r="J15" s="22" t="inlineStr"/>
+      <c r="K15" s="22" t="inlineStr"/>
+      <c r="L15" s="22" t="inlineStr"/>
+      <c r="M15" s="22" t="inlineStr"/>
+      <c r="N15" s="22" t="inlineStr"/>
+      <c r="O15" s="22" t="inlineStr"/>
+      <c r="P15" s="22" t="inlineStr"/>
+      <c r="Q15" s="22" t="inlineStr"/>
+      <c r="R15" s="22" t="inlineStr"/>
+      <c r="S15" s="22" t="inlineStr"/>
+      <c r="T15" s="22" t="inlineStr"/>
+      <c r="U15" s="22" t="inlineStr"/>
+      <c r="V15" s="22" t="inlineStr"/>
+      <c r="W15" s="22" t="inlineStr"/>
+      <c r="X15" s="22" t="inlineStr"/>
+      <c r="Y15" s="22" t="inlineStr"/>
+      <c r="Z15" s="22" t="inlineStr"/>
+      <c r="AA15" s="22" t="inlineStr"/>
+      <c r="AB15" s="22" t="inlineStr"/>
+      <c r="AC15" s="22" t="inlineStr"/>
+      <c r="AD15" s="22" t="inlineStr"/>
+      <c r="AE15" s="22" t="inlineStr"/>
+      <c r="AF15" s="22" t="inlineStr"/>
+      <c r="AG15" s="22" t="inlineStr"/>
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="B16" s="5" t="n"/>
@@ -2196,7 +2135,7 @@
       </c>
     </row>
     <row r="18" ht="261.75" customHeight="1">
-      <c r="B18" s="32" t="inlineStr"/>
+      <c r="B18" s="41" t="inlineStr"/>
     </row>
     <row r="19" ht="23.25" customHeight="1"/>
     <row r="20" ht="23.25" customHeight="1">

--- a/FM-MN-07_WELDING_ALUMINUM-01.xlsx
+++ b/FM-MN-07_WELDING_ALUMINUM-01.xlsx
@@ -1717,7 +1717,11 @@
       <c r="E6" s="9" t="inlineStr"/>
       <c r="F6" s="9" t="inlineStr"/>
       <c r="G6" s="9" t="inlineStr"/>
-      <c r="H6" s="9" t="inlineStr"/>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I6" s="9" t="inlineStr"/>
       <c r="J6" s="9" t="inlineStr"/>
       <c r="K6" s="9" t="inlineStr"/>
@@ -1758,7 +1762,11 @@
       <c r="E7" s="9" t="inlineStr"/>
       <c r="F7" s="9" t="inlineStr"/>
       <c r="G7" s="9" t="inlineStr"/>
-      <c r="H7" s="9" t="inlineStr"/>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I7" s="9" t="inlineStr"/>
       <c r="J7" s="9" t="inlineStr"/>
       <c r="K7" s="9" t="inlineStr"/>
@@ -1799,7 +1807,11 @@
       <c r="E8" s="9" t="inlineStr"/>
       <c r="F8" s="9" t="inlineStr"/>
       <c r="G8" s="9" t="inlineStr"/>
-      <c r="H8" s="9" t="inlineStr"/>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I8" s="9" t="inlineStr"/>
       <c r="J8" s="9" t="inlineStr"/>
       <c r="K8" s="9" t="inlineStr"/>
@@ -1840,7 +1852,11 @@
       <c r="E9" s="9" t="inlineStr"/>
       <c r="F9" s="9" t="inlineStr"/>
       <c r="G9" s="9" t="inlineStr"/>
-      <c r="H9" s="9" t="inlineStr"/>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I9" s="9" t="inlineStr"/>
       <c r="J9" s="9" t="inlineStr"/>
       <c r="K9" s="9" t="inlineStr"/>
@@ -1881,7 +1897,11 @@
       <c r="E10" s="9" t="inlineStr"/>
       <c r="F10" s="9" t="inlineStr"/>
       <c r="G10" s="9" t="inlineStr"/>
-      <c r="H10" s="9" t="inlineStr"/>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I10" s="9" t="inlineStr"/>
       <c r="J10" s="9" t="inlineStr"/>
       <c r="K10" s="9" t="inlineStr"/>
@@ -1922,7 +1942,11 @@
       <c r="E11" s="9" t="inlineStr"/>
       <c r="F11" s="9" t="inlineStr"/>
       <c r="G11" s="9" t="inlineStr"/>
-      <c r="H11" s="9" t="inlineStr"/>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I11" s="9" t="inlineStr"/>
       <c r="J11" s="9" t="inlineStr"/>
       <c r="K11" s="9" t="inlineStr"/>
@@ -1963,7 +1987,11 @@
       <c r="E12" s="9" t="inlineStr"/>
       <c r="F12" s="9" t="inlineStr"/>
       <c r="G12" s="9" t="inlineStr"/>
-      <c r="H12" s="9" t="inlineStr"/>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="I12" s="9" t="inlineStr"/>
       <c r="J12" s="9" t="inlineStr"/>
       <c r="K12" s="9" t="inlineStr"/>
@@ -1998,7 +2026,11 @@
       <c r="E13" s="38" t="inlineStr"/>
       <c r="F13" s="38" t="inlineStr"/>
       <c r="G13" s="38" t="inlineStr"/>
-      <c r="H13" s="38" t="inlineStr"/>
+      <c r="H13" s="40" t="inlineStr">
+        <is>
+          <t>อินทัช เป็นสุข</t>
+        </is>
+      </c>
       <c r="I13" s="38" t="inlineStr"/>
       <c r="J13" s="38" t="inlineStr"/>
       <c r="K13" s="38" t="inlineStr"/>

--- a/FM-MN-07_WELDING_ALUMINUM-01.xlsx
+++ b/FM-MN-07_WELDING_ALUMINUM-01.xlsx
@@ -1722,7 +1722,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr"/>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J6" s="9" t="inlineStr"/>
       <c r="K6" s="9" t="inlineStr"/>
       <c r="L6" s="9" t="inlineStr"/>
@@ -1767,7 +1771,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr"/>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J7" s="9" t="inlineStr"/>
       <c r="K7" s="9" t="inlineStr"/>
       <c r="L7" s="9" t="inlineStr"/>
@@ -1812,7 +1820,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr"/>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J8" s="9" t="inlineStr"/>
       <c r="K8" s="9" t="inlineStr"/>
       <c r="L8" s="9" t="inlineStr"/>
@@ -1857,7 +1869,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr"/>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J9" s="9" t="inlineStr"/>
       <c r="K9" s="9" t="inlineStr"/>
       <c r="L9" s="9" t="inlineStr"/>
@@ -1902,7 +1918,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr"/>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J10" s="9" t="inlineStr"/>
       <c r="K10" s="9" t="inlineStr"/>
       <c r="L10" s="9" t="inlineStr"/>
@@ -1947,7 +1967,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I11" s="9" t="inlineStr"/>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J11" s="9" t="inlineStr"/>
       <c r="K11" s="9" t="inlineStr"/>
       <c r="L11" s="9" t="inlineStr"/>
@@ -1992,7 +2016,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr"/>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="J12" s="9" t="inlineStr"/>
       <c r="K12" s="9" t="inlineStr"/>
       <c r="L12" s="9" t="inlineStr"/>
@@ -2031,7 +2059,11 @@
           <t>อินทัช เป็นสุข</t>
         </is>
       </c>
-      <c r="I13" s="38" t="inlineStr"/>
+      <c r="I13" s="40" t="inlineStr">
+        <is>
+          <t>อินทัช เป็นสุข</t>
+        </is>
+      </c>
       <c r="J13" s="38" t="inlineStr"/>
       <c r="K13" s="38" t="inlineStr"/>
       <c r="L13" s="38" t="inlineStr"/>

--- a/FM-MN-07_WELDING_ALUMINUM-01.xlsx
+++ b/FM-MN-07_WELDING_ALUMINUM-01.xlsx
@@ -1727,7 +1727,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J6" s="9" t="inlineStr"/>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K6" s="9" t="inlineStr"/>
       <c r="L6" s="9" t="inlineStr"/>
       <c r="M6" s="9" t="inlineStr"/>
@@ -1776,7 +1780,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J7" s="9" t="inlineStr"/>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K7" s="9" t="inlineStr"/>
       <c r="L7" s="9" t="inlineStr"/>
       <c r="M7" s="9" t="inlineStr"/>
@@ -1825,7 +1833,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J8" s="9" t="inlineStr"/>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K8" s="9" t="inlineStr"/>
       <c r="L8" s="9" t="inlineStr"/>
       <c r="M8" s="9" t="inlineStr"/>
@@ -1874,7 +1886,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J9" s="9" t="inlineStr"/>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K9" s="9" t="inlineStr"/>
       <c r="L9" s="9" t="inlineStr"/>
       <c r="M9" s="9" t="inlineStr"/>
@@ -1923,7 +1939,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J10" s="9" t="inlineStr"/>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K10" s="9" t="inlineStr"/>
       <c r="L10" s="9" t="inlineStr"/>
       <c r="M10" s="9" t="inlineStr"/>
@@ -1972,7 +1992,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J11" s="9" t="inlineStr"/>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K11" s="9" t="inlineStr"/>
       <c r="L11" s="9" t="inlineStr"/>
       <c r="M11" s="9" t="inlineStr"/>
@@ -2021,7 +2045,11 @@
           <t>/</t>
         </is>
       </c>
-      <c r="J12" s="9" t="inlineStr"/>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="K12" s="9" t="inlineStr"/>
       <c r="L12" s="9" t="inlineStr"/>
       <c r="M12" s="9" t="inlineStr"/>
@@ -2064,7 +2092,11 @@
           <t>อินทัช เป็นสุข</t>
         </is>
       </c>
-      <c r="J13" s="38" t="inlineStr"/>
+      <c r="J13" s="40" t="inlineStr">
+        <is>
+          <t>อินทัช เป็นสุข</t>
+        </is>
+      </c>
       <c r="K13" s="38" t="inlineStr"/>
       <c r="L13" s="38" t="inlineStr"/>
       <c r="M13" s="38" t="inlineStr"/>

--- a/FM-MN-07_WELDING_ALUMINUM-01.xlsx
+++ b/FM-MN-07_WELDING_ALUMINUM-01.xlsx
@@ -1733,7 +1733,11 @@
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr"/>
-      <c r="L6" s="9" t="inlineStr"/>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M6" s="9" t="inlineStr"/>
       <c r="N6" s="9" t="inlineStr"/>
       <c r="O6" s="9" t="inlineStr"/>
@@ -1786,7 +1790,11 @@
         </is>
       </c>
       <c r="K7" s="9" t="inlineStr"/>
-      <c r="L7" s="9" t="inlineStr"/>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M7" s="9" t="inlineStr"/>
       <c r="N7" s="9" t="inlineStr"/>
       <c r="O7" s="9" t="inlineStr"/>
@@ -1839,7 +1847,11 @@
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr"/>
-      <c r="L8" s="9" t="inlineStr"/>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M8" s="9" t="inlineStr"/>
       <c r="N8" s="9" t="inlineStr"/>
       <c r="O8" s="9" t="inlineStr"/>
@@ -1892,7 +1904,11 @@
         </is>
       </c>
       <c r="K9" s="9" t="inlineStr"/>
-      <c r="L9" s="9" t="inlineStr"/>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M9" s="9" t="inlineStr"/>
       <c r="N9" s="9" t="inlineStr"/>
       <c r="O9" s="9" t="inlineStr"/>
@@ -1945,7 +1961,11 @@
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr"/>
-      <c r="L10" s="9" t="inlineStr"/>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M10" s="9" t="inlineStr"/>
       <c r="N10" s="9" t="inlineStr"/>
       <c r="O10" s="9" t="inlineStr"/>
@@ -1998,7 +2018,11 @@
         </is>
       </c>
       <c r="K11" s="9" t="inlineStr"/>
-      <c r="L11" s="9" t="inlineStr"/>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M11" s="9" t="inlineStr"/>
       <c r="N11" s="9" t="inlineStr"/>
       <c r="O11" s="9" t="inlineStr"/>
@@ -2051,7 +2075,11 @@
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr"/>
-      <c r="L12" s="9" t="inlineStr"/>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>/</t>
+        </is>
+      </c>
       <c r="M12" s="9" t="inlineStr"/>
       <c r="N12" s="9" t="inlineStr"/>
       <c r="O12" s="9" t="inlineStr"/>
@@ -2098,7 +2126,11 @@
         </is>
       </c>
       <c r="K13" s="38" t="inlineStr"/>
-      <c r="L13" s="38" t="inlineStr"/>
+      <c r="L13" s="40" t="inlineStr">
+        <is>
+          <t>อนุสรณ์  ชื่นแฉ่ง</t>
+        </is>
+      </c>
       <c r="M13" s="38" t="inlineStr"/>
       <c r="N13" s="38" t="inlineStr"/>
       <c r="O13" s="38" t="inlineStr"/>
